--- a/AAII_Financials/Quarterly/DEO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DEO_QTR_FIN.xlsx
@@ -656,24 +656,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -684,352 +684,378 @@
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42185</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4591500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4591500</v>
+      </c>
+      <c r="F8" s="3">
         <v>5230000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>5230000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>4672000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>4672000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>5450500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>5450500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>4653500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>4653500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>5481000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>5481000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4717500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>4717500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>5560000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>6874000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>5647200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>8933800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>6979800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>8427100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>7498100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>9240700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>7494500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>7908100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>6363700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>7312000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>6469400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>7769100</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1920500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1920500</v>
+      </c>
+      <c r="F9" s="3">
         <v>2026000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2026000</v>
       </c>
-      <c r="F9" s="3">
-        <v>1923500</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1923500</v>
-      </c>
       <c r="H9" s="3">
+        <v>1934500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1934500</v>
+      </c>
+      <c r="J9" s="3">
         <v>2070500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>2070500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1891500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1891500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>2107000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2095500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1965000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>1965000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>2139500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>2661000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2421700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>3352600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>2761900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>3059500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2921800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>3451500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>2949100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>3035900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2555100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>2989500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>2853500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>3184000</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2671000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2671000</v>
+      </c>
+      <c r="F10" s="3">
         <v>3204000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>3204000</v>
       </c>
-      <c r="F10" s="3">
-        <v>2748500</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2748500</v>
-      </c>
       <c r="H10" s="3">
+        <v>2737500</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2737500</v>
+      </c>
+      <c r="J10" s="3">
         <v>3380000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>3380000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2762000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>2762000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>3374000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>3385500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>2752500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>2752500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>3420500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>4213000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>3225600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>5581100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>4217900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>5367600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>4576300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>5789200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>4545400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>4872200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>3808600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>4322500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>3615900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>4585100</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1059,52 +1085,54 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>35500</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>37000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>37000</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>34500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>34500</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>31500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>31500</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>8</v>
@@ -1142,8 +1170,14 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1225,139 +1259,151 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1211000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1211000</v>
+      </c>
+      <c r="F14" s="3">
         <v>63000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>63000</v>
       </c>
-      <c r="F14" s="3">
-        <v>755000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>755000</v>
-      </c>
       <c r="H14" s="3">
+        <v>617500</v>
+      </c>
+      <c r="I14" s="3">
+        <v>617500</v>
+      </c>
+      <c r="J14" s="3">
         <v>122000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>122000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-26500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-26500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>23500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>35000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>202000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>202000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>12000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>1623900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>73200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>12900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-152500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>170400</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>55900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>-24600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>197000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>-139600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>-233100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>96100</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>128500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>128500</v>
+      </c>
+      <c r="F15" s="3">
         <v>208000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>208000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>79500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>79500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>194500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>194500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>43500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>43500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>205500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>205500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>51500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>51500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>166000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
@@ -1391,8 +1437,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1419,174 +1471,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3350000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3350000</v>
+      </c>
+      <c r="F17" s="3">
         <v>3593500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3593500</v>
       </c>
-      <c r="F17" s="3">
-        <v>3395000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>3395000</v>
-      </c>
       <c r="H17" s="3">
+        <v>3503500</v>
+      </c>
+      <c r="I17" s="3">
+        <v>3503500</v>
+      </c>
+      <c r="J17" s="3">
         <v>3756000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3756000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3335000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3335000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3800000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3788500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>3413000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>3413000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>3681500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>4630000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>6054100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>5903700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>5104500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>5284600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>5500100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>6141600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>5505300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>5340200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>4876800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>4932900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>4620600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>5443600</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1241500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1241500</v>
+      </c>
+      <c r="F18" s="3">
         <v>1636500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1636500</v>
       </c>
-      <c r="F18" s="3">
-        <v>1277000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1277000</v>
-      </c>
       <c r="H18" s="3">
+        <v>1168500</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1168500</v>
+      </c>
+      <c r="J18" s="3">
         <v>1694500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1694500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1318500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>1318500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1681000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1692500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1304500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1304500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1878500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>2244000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-406900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>3030000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1875300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>3142500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1998000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>3099100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>1989100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>2567900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>1486900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>2379100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>1848800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>2325500</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1616,423 +1682,455 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="F20" s="3">
         <v>-38000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-38000</v>
       </c>
-      <c r="F20" s="3">
-        <v>-32000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-32000</v>
-      </c>
       <c r="H20" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-50000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-50000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-70500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-70500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-116000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-116000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-105500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-105500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-95500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>199000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>199700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>363600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>305700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>335500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>295500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>314200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>274300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>277100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>206100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>254300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>181700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>201500</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1411000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1411000</v>
+      </c>
+      <c r="F21" s="3">
         <v>1882500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>1882500</v>
       </c>
-      <c r="F21" s="3">
-        <v>1388500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1388500</v>
-      </c>
       <c r="H21" s="3">
+        <v>1279000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1279000</v>
+      </c>
+      <c r="J21" s="3">
         <v>1939000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1939000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>1432500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>1432500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>2002500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2014000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1461500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>1461500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>2140000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>2662000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1719500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>3748500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>2402300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>3703600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>2700800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>3677900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>2507000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>3064200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>1943400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>2999900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>2359700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>2777100</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>230000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>230000</v>
+      </c>
+      <c r="F22" s="3">
         <v>298000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>298000</v>
       </c>
-      <c r="F22" s="3">
-        <v>276500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>276500</v>
-      </c>
       <c r="H22" s="3">
+        <v>219500</v>
+      </c>
+      <c r="I22" s="3">
+        <v>219500</v>
+      </c>
+      <c r="J22" s="3">
         <v>321500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>321500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>262500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>262500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>343500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>343500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>219000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>219000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>310500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>245000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>315100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>336300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>297500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>273300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>248900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>294300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>286300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>290700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>292200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>306500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>327900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>367400</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-114500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-114500</v>
+      </c>
+      <c r="F23" s="3">
         <v>1396500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>1396500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>381500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>381500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1387000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>1387000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1190500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1190500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1539500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1539500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1017500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1017500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1803500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>2198000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-522300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>3057300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1883500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>3204700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>2044600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>3118900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>1977100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>2554300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>1400800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>2326900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>1702600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>2159500</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="F24" s="3">
         <v>341500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>341500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>150000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>150000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>349500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>349500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>278500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>278500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>368500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>368500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>198500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>198500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>383000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>537000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>73200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>657600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>395900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>683100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>682900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>618400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>394100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>537000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>260900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>386100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>250200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>363400</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2114,174 +2212,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="F26" s="3">
         <v>1055000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>1055000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>231500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>231500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1037500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>1037500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>912000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>912000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1171000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1171000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>819000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>819000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1420500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1661000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-595500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2399700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1487600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>2521500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>1361700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>2500500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>1583000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>2017400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>1140000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>1940800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>1452400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>1796100</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-129000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-129000</v>
+      </c>
+      <c r="F27" s="3">
         <v>997500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>997500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>209500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>209500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>967500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>967500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>830000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>830000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1105000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1105000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>868000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>868000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1354500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1580000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-565700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>2314100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1386800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>2410500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>1291200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>2402900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>1528400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>1932400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>1093000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>1833900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>1409000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>1726300</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2363,8 +2479,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2407,47 +2529,53 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>-8000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>509400</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-67700</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2529,8 +2657,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2612,174 +2746,192 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>41000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>41000</v>
+      </c>
+      <c r="F32" s="3">
         <v>38000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>38000</v>
       </c>
-      <c r="F32" s="3">
-        <v>32000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>32000</v>
-      </c>
       <c r="H32" s="3">
+        <v>31000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>31000</v>
+      </c>
+      <c r="J32" s="3">
         <v>50000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>50000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>70500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>70500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>116000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>116000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>105500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>105500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>95500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-199000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-199700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-363600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-305700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-335500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-295500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-314200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-274300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-277100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-206100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-254300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-181700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-201500</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-129000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-129000</v>
+      </c>
+      <c r="F33" s="3">
         <v>997500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>997500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>209500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>209500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>967500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>967500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>830000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>830000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1105000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1105000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>868000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>868000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1354500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1580000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-565700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>2314100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1386800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>2410500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>1283200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>2912300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>1528400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>1864600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>1093000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>1833900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>1409000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>1726300</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2861,179 +3013,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-129000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-129000</v>
+      </c>
+      <c r="F35" s="3">
         <v>997500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>997500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>209500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>209500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>967500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>967500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>830000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>830000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1105000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1105000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>868000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>868000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1354500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1580000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-565700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>2314100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1386800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>2410500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>1283200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>2912300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>1528400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>1864600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>1093000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>1833900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>1409000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>1726300</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42185</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3063,8 +3233,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3094,755 +3266,811 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1520000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1520000</v>
+      </c>
+      <c r="F41" s="3">
         <v>2209000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2209000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2200000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2200000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1656000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1656000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1130000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1130000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1529000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1529000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1813000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1813000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>3332700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2763000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>4122500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1178800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>1091700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>1940900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1163400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1301900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>1585700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1544400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1420400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>705600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>621500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>1056100</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>261000</v>
       </c>
       <c r="F42" s="3">
-        <v>447000</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>447000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>318000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>318000</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>275000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>275000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>249000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>249000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
         <v>84000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>93000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>52100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>148800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>14600</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>46600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>174100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>107800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>155200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>645600</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>288300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>60600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>150100</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3447000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3447000</v>
+      </c>
+      <c r="F43" s="3">
         <v>4541000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>4541000</v>
       </c>
-      <c r="F43" s="3">
-        <v>3725000</v>
-      </c>
-      <c r="G43" s="3">
-        <v>3725000</v>
-      </c>
       <c r="H43" s="3">
+        <v>3813000</v>
+      </c>
+      <c r="I43" s="3">
+        <v>3813000</v>
+      </c>
+      <c r="J43" s="3">
         <v>4767000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>4767000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3517000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3517000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4854000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4854000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>3431000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3431000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4867800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>3248000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2854600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>4535100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>3252700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>4334300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>3651200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>5006700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>3451000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>4437500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>3503400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>4013400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>3206400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>4558700</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10529000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>10529000</v>
+      </c>
+      <c r="F44" s="3">
         <v>10556000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>10556000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>10658000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>10658000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>9699000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>9699000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>9720000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>9720000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>9840000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>9840000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>9653000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>9653000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>9099300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>5750000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>7160700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>6773500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>6409400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>6436200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>6675500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>6960900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>6374700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>5839000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>5972400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>5722000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>6023000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>6053300</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1295000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1295000</v>
+      </c>
+      <c r="F45" s="3">
         <v>1588000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1588000</v>
       </c>
-      <c r="F45" s="3">
-        <v>334000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>334000</v>
-      </c>
       <c r="H45" s="3">
+        <v>375000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>375000</v>
+      </c>
+      <c r="J45" s="3">
         <v>642000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>642000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>210000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>210000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>564000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>564000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>188000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>188000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>698800</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
       <c r="S45" s="3">
+        <v>0</v>
+      </c>
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
         <v>63300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>76100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>101300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>31900</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
       <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3">
         <v>3700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>3900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>734300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>188300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>428000</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17212000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>17212000</v>
+      </c>
+      <c r="F46" s="3">
         <v>18894000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>18894000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>17497000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>17497000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>16764000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>16764000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>15126000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>15126000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>16787000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>16787000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>15622000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>15622000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>17998700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>11845000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>14230900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>12602800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>10978600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>12827200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>11568600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>13443500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>11519300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>11979800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>11545800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>11463600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>10099800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>12246100</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5312000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>5312000</v>
+      </c>
+      <c r="F47" s="3">
         <v>5454000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>5454000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>5381000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>5381000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>5178000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>5178000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>5126000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>5126000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>5325000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>5325000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>4896000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>4896000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>4779800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>4065000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>5371800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>4515300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>4309200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>4413600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>4370000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>4729300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>4233900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>3953400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>3945500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>3457700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>3322300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>3928000</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8996000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>8996000</v>
+      </c>
+      <c r="F48" s="3">
         <v>9246000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>9246000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>9528000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>9528000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>8533000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>8533000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>8509000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>8509000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>8212000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>8212000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>7738000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>7738000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>7195600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>4820000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>6174500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>6050100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>5258000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>5201700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>5473500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>5623600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>5372200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>4928900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>5075100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>4738600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>4944500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>5030100</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13375000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>13375000</v>
+      </c>
+      <c r="F49" s="3">
         <v>14694000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>14694000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>14776000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>14776000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>14764000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>14764000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>14814000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>14814000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>14496000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>14496000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>14506000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>14506000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>14615300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>10877000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>14018800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>14933000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>14708000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>15315800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>16734600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>18123300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>16730400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>15901200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>16134300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>14781700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>14788900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>14983800</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3924,8 +4152,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4007,91 +4241,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1777000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1777000</v>
+      </c>
+      <c r="F52" s="3">
         <v>1846000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1846000</v>
       </c>
-      <c r="F52" s="3">
-        <v>1989000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1989000</v>
-      </c>
       <c r="H52" s="3">
+        <v>1990000</v>
+      </c>
+      <c r="I52" s="3">
+        <v>1990000</v>
+      </c>
+      <c r="J52" s="3">
         <v>1576000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1576000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1756000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1756000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1774000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1774000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1941000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1941000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1935100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1197000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1525900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1273100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1403200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1393100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1407000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>677800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>552500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>468000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>460400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>510000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>823000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>563600</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4173,91 +4419,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>46845000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>46845000</v>
+      </c>
+      <c r="F54" s="3">
         <v>50272000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>50272000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>49322000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>49322000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>46946000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>46946000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>45474000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>45474000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>46765000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>46765000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>44883000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>44883000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>46652200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>32804000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>41321900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>39374300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>36657000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>39151500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>39553600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>42597600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>38408200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>37231300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>37161100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>34951600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>33978400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>36751600</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4287,8 +4545,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4318,506 +4578,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2827000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2827000</v>
+      </c>
+      <c r="F57" s="3">
         <v>7035000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>7035000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3123000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3123000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>7094000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>7094000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3071000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3071000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>7292000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>7292000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3351000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3351000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>7361900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>4624000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>4569100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5551300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>4921800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>5385900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>5257800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>5861400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>4743800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>4851300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>4398100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>4166000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>3875300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>4341500</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2567000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2567000</v>
+      </c>
+      <c r="F58" s="3">
         <v>3303000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>3303000</v>
       </c>
-      <c r="F58" s="3">
-        <v>3048000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>3048000</v>
-      </c>
       <c r="H58" s="3">
+        <v>3040000</v>
+      </c>
+      <c r="I58" s="3">
+        <v>3040000</v>
+      </c>
+      <c r="J58" s="3">
         <v>2496000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2496000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2996000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2996000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2004000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2004000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>2244000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>2244000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>2777300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1214000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>2475000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>4195100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>2294600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>2125100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>2433300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>3365100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>3273900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>3378300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>2684300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>2523800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>2529600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>3746300</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2393000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2393000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1438000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1438000</v>
       </c>
-      <c r="F59" s="3">
-        <v>1584000</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1584000</v>
-      </c>
       <c r="H59" s="3">
+        <v>1592000</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1592000</v>
+      </c>
+      <c r="J59" s="3">
         <v>881000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>881000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1155000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1155000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1334000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1334000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1354000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1354000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1332600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>872000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>1014800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>1238300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>986200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>1184500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>774700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>1037300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>849400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1087500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>987400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>875200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>561000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>886200</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10730000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>10730000</v>
+      </c>
+      <c r="F60" s="3">
         <v>11776000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>11776000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>10712000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>10712000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>10471000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>10471000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>9868000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>9868000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>10630000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>10630000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>9593000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>9593000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>11471800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>6710000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>8058900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>10984800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>8202600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>8695400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>8465800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>10263800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>8867100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>9317100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>8069800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>7565000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>6965800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>8973900</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19629000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>19629000</v>
+      </c>
+      <c r="F61" s="3">
         <v>20987000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>20987000</v>
       </c>
-      <c r="F61" s="3">
-        <v>21563000</v>
-      </c>
-      <c r="G61" s="3">
-        <v>21563000</v>
-      </c>
       <c r="H61" s="3">
+        <v>21361000</v>
+      </c>
+      <c r="I61" s="3">
+        <v>21361000</v>
+      </c>
+      <c r="J61" s="3">
         <v>20097000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>20097000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>19485000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>19485000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>20341000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>20341000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>19587000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>19587000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>19368600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>14063000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>18348500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>12520900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>12411100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>12530800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>10747300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>10821300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>8764600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>9239500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>10527100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>10343200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>11008400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>11216400</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>690000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>690000</v>
+      </c>
+      <c r="F62" s="3">
         <v>509000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>509000</v>
       </c>
-      <c r="F62" s="3">
-        <v>516000</v>
-      </c>
-      <c r="G62" s="3">
-        <v>516000</v>
-      </c>
       <c r="H62" s="3">
+        <v>718000</v>
+      </c>
+      <c r="I62" s="3">
+        <v>718000</v>
+      </c>
+      <c r="J62" s="3">
         <v>603000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>603000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>675000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>675000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>760000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>760000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>772000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>772000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>745800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3653000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>4443800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>4416000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>4147600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>4344100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>4749400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>4969900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>4762400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>4815600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>5286400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>4421600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>3816100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>5110500</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4899,8 +5197,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4982,8 +5286,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5065,91 +5375,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33891000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>33891000</v>
+      </c>
+      <c r="F66" s="3">
         <v>36578000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>36578000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>36144000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>36144000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>34541000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>34541000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>33404000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>33404000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>35041000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>35041000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>33174000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>33174000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>34764700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>25986000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>32920600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>30039800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>26863800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>27725900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>26311900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>28556900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>24677500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>25563100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>26035300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>24335800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>23745700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>27233900</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5179,8 +5501,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5262,8 +5586,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5345,8 +5675,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5428,8 +5764,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5511,91 +5853,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>10502000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>10502000</v>
+      </c>
+      <c r="F72" s="3">
         <v>10905000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>10905000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>10274000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>10274000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>10389000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>10389000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>9783000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>9783000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>8949000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>8949000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>8876000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>8876000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>6864300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>7986000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>9359100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>10734200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>10661200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>12388100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>14632800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>15237900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>14375100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>12210100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>11864000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>12143100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>11861600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>9648100</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5677,8 +6031,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5760,8 +6120,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5843,91 +6209,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10871000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>10871000</v>
+      </c>
+      <c r="F76" s="3">
         <v>11601000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>11601000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11090000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>11090000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>10284000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>10284000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>10032000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>10032000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>9791000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>9791000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>9856000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>9856000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>9806600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>6818000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>8401300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>9334500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>9793200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>11425600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>13241800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>14040700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>13730700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>11668200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>11125800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>10615800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>10232800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>9517800</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6009,179 +6387,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42185</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-129000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-129000</v>
+      </c>
+      <c r="F81" s="3">
         <v>997500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>997500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>209500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>209500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>967500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>967500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>830000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>830000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1105000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1105000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>868000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>868000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1354500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1580000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-565700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>2314100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1386800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>2410500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>1283200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>2912300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>1528400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>1864600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>1093000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>1833900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>1409000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>1726300</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6211,91 +6607,99 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>132500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>132500</v>
+      </c>
+      <c r="F83" s="3">
         <v>194500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>194500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
+        <v>160000</v>
+      </c>
+      <c r="I83" s="3">
         <v>94500</v>
       </c>
-      <c r="G83" s="3">
-        <v>94500</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>205500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>205500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>156500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>98500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>166000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>166000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>243200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>146600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>151700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>219000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>1926700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>354900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>221400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>225700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>407300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>264600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>243600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>219200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>250400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>366500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>329200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>250200</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6377,8 +6781,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6460,8 +6870,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6543,8 +6959,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6626,8 +7048,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6709,91 +7137,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1134500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1134500</v>
+      </c>
+      <c r="F89" s="3">
         <v>1061500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1061500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>986000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>986000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1162500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1162500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>979500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>979500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1073000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1073000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>1082000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>1082000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>736000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1998000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>1280300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1598200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1925600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1956700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>2443900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1766100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>2483100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>1560400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>1970800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1352600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>2099000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>1260200</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6823,91 +7263,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-296000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-296000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-302500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-302500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-490000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-490000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-316000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-316000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-464000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-464000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-291000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-291000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-451500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-451500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-257000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-326400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-370000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-330000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-468500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-330600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-497800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-297200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-427400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-242600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-393900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-266100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-484600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-355500</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6989,8 +7437,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7072,91 +7526,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-295500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-295500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-195500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-195500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-544000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-544000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-316000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-316000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-437500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-437500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-360000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-360000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-431000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-431000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-282000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-604000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-467700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-531100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-467300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>157400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-496500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-1101000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-450000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-263600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>197000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>580400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>36900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-1214100</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7186,91 +7652,99 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>222500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>222500</v>
+      </c>
+      <c r="F96" s="3">
         <v>700500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>700500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>449500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>449500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>699500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>699500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>447000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>447000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>674000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>674000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>435500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>435500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>597000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-992000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-794000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-1248200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-737900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-1211400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-816000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-1369800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-792200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-1133100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-739500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-1142600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-711100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-1054700</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7352,8 +7826,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7435,8 +7915,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7518,253 +8004,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1158500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-1158500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-733500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-733500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-197500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-197500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-549500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-549500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-719500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-719500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-833500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-833500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1383000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1383000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-137500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1631000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>2192100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-905800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-2205600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-1269900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-1923400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-952400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-2042400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-1138000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-1869100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-1784300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-2418900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>135600</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>16500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-34000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-34000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-22500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-22500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-25500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-25500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-12500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-12500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-190200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>147900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>9500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-236000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-109200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-39700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-46900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>17100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-14600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-39600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-62600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>40600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>147400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-37800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-115900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>19800</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-331500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-331500</v>
+      </c>
+      <c r="F102" s="3">
         <v>135500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>135500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>261000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>261000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>263000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>263000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-171500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-171500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-143000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-143000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-757500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-757500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>304000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-473000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>2895600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>121600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-794100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>861200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>9300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-326900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-71900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>199500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>446100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>110900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-399000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>201500</v>
       </c>
     </row>
